--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-luftfeuchtigkeit.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-luftfeuchtigkeit.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01</t>
+    <t>2026-09-02</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-luftfeuchtigkeit.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-luftfeuchtigkeit.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-luftfeuchtigkeit.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-luftfeuchtigkeit.xlsx
@@ -988,6 +988,14 @@
     <t>Ein Verweis auf einen von SNOMED CT definierten Code</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://snomed.info/sct"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
+  &lt;code value="3525006"/&gt;
+  &lt;display value="Humidity (physical force)"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>Observation.code.coding:sct.id</t>
   </si>
   <si>
@@ -1001,9 +1009,6 @@
   </si>
   <si>
     <t>Observation.code.coding:sct.code</t>
-  </si>
-  <si>
-    <t>3525006</t>
   </si>
   <si>
     <t>Observation.code.coding:sct.display</t>
@@ -6660,7 +6665,7 @@
         <v>81</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>81</v>
+        <v>312</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>81</v>
@@ -6731,7 +6736,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>273</v>
@@ -6846,7 +6851,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>274</v>
@@ -6963,7 +6968,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>275</v>
@@ -7082,7 +7087,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>282</v>
@@ -7199,7 +7204,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>288</v>
@@ -7245,7 +7250,7 @@
         <v>81</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>317</v>
+        <v>81</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>81</v>
